--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251115_201455.xlsx
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
